--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -5574,7 +5574,7 @@
         <v>42973</v>
       </c>
       <c r="K56" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -2230,7 +2230,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -5556,7 +5556,7 @@
         <v>0.003383487993130568</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>244817</v>
@@ -9104,7 +9104,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>50942</v>

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -2230,7 +2230,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -5556,7 +5556,7 @@
         <v>0.003383487993130568</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>244817</v>
@@ -9104,7 +9104,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>50942</v>

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -5574,7 +5574,7 @@
         <v>42973</v>
       </c>
       <c r="K56" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -5574,7 +5574,7 @@
         <v>42973</v>
       </c>
       <c r="K56" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -5574,7 +5574,7 @@
         <v>42973</v>
       </c>
       <c r="K56" t="n">
-        <v>93</v>
+        <v>105</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -5574,7 +5574,7 @@
         <v>42973</v>
       </c>
       <c r="K56" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="57">
@@ -9122,7 +9122,7 @@
         <v>9114</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -5574,7 +5574,7 @@
         <v>42973</v>
       </c>
       <c r="K56" t="n">
-        <v>107</v>
+        <v>115</v>
       </c>
     </row>
     <row r="57">
@@ -9119,10 +9119,10 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>9114</v>
+        <v>9117</v>
       </c>
       <c r="K56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -5574,7 +5574,7 @@
         <v>42973</v>
       </c>
       <c r="K56" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="57">
@@ -9122,7 +9122,7 @@
         <v>9117</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -2230,7 +2230,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -2248,7 +2248,7 @@
         <v>453</v>
       </c>
       <c r="K43" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="44">
@@ -5556,7 +5556,7 @@
         <v>0.003383487993130568</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>244817</v>
@@ -5571,10 +5571,10 @@
         <v>0.0002940972236405152</v>
       </c>
       <c r="J56" t="n">
-        <v>42973</v>
+        <v>43121</v>
       </c>
       <c r="K56" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -9104,7 +9104,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>50942</v>
@@ -9119,10 +9119,10 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>9117</v>
+        <v>9137</v>
       </c>
       <c r="K56" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -9119,10 +9119,10 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>9137</v>
+        <v>9138</v>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -2230,7 +2230,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -5556,7 +5556,7 @@
         <v>0.003383487993130568</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F56" t="n">
         <v>244817</v>
@@ -9104,7 +9104,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F56" t="n">
         <v>50942</v>

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -5571,7 +5571,7 @@
         <v>0.0002940972236405152</v>
       </c>
       <c r="J56" t="n">
-        <v>43121</v>
+        <v>43119</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -624,7 +624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K76"/>
+  <dimension ref="A1:K77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2439,20 +2439,20 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>09/2020</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0</v>
+        <v>10983</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -2467,10 +2467,10 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>289</v>
+        <v>453</v>
       </c>
       <c r="K49" t="n">
-        <v>163</v>
+        <v>47</v>
       </c>
     </row>
     <row r="50">
@@ -2486,7 +2486,7 @@
         <v>0</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E50" t="n">
         <v>7</v>
@@ -2513,11 +2513,11 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>09/2021</t>
+          <t>09/2020</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>10983</v>
+        <v>0</v>
       </c>
       <c r="C51" t="n">
         <v>0</v>
@@ -2541,16 +2541,16 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>453</v>
+        <v>289</v>
       </c>
       <c r="K51" t="n">
-        <v>12</v>
+        <v>163</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>09/2022</t>
+          <t>09/2021</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -2563,7 +2563,7 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -2581,13 +2581,13 @@
         <v>453</v>
       </c>
       <c r="K52" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>09/2023</t>
+          <t>09/2022</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2600,7 +2600,7 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -2618,13 +2618,13 @@
         <v>453</v>
       </c>
       <c r="K53" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>09/2024</t>
+          <t>09/2023</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -2637,7 +2637,7 @@
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -2655,13 +2655,13 @@
         <v>453</v>
       </c>
       <c r="K54" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>09/2025</t>
+          <t>09/2024</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -2692,26 +2692,26 @@
         <v>453</v>
       </c>
       <c r="K55" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>10/2020</t>
+          <t>09/2025</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0</v>
+        <v>10983</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -2726,10 +2726,10 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>289</v>
+        <v>453</v>
       </c>
       <c r="K56" t="n">
-        <v>164</v>
+        <v>42</v>
       </c>
     </row>
     <row r="57">
@@ -2745,7 +2745,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E57" t="n">
         <v>5</v>
@@ -2772,11 +2772,11 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>10/2021</t>
+          <t>10/2020</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>10983</v>
+        <v>0</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
@@ -2785,7 +2785,7 @@
         <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -2800,16 +2800,16 @@
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>453</v>
+        <v>289</v>
       </c>
       <c r="K58" t="n">
-        <v>15</v>
+        <v>164</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>10/2022</t>
+          <t>10/2021</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -2822,7 +2822,7 @@
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -2840,13 +2840,13 @@
         <v>453</v>
       </c>
       <c r="K59" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>10/2023</t>
+          <t>10/2022</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -2859,7 +2859,7 @@
         <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -2877,13 +2877,13 @@
         <v>453</v>
       </c>
       <c r="K60" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>10/2024</t>
+          <t>10/2023</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -2896,7 +2896,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -2914,13 +2914,13 @@
         <v>453</v>
       </c>
       <c r="K61" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>10/2025</t>
+          <t>10/2024</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -2951,13 +2951,13 @@
         <v>453</v>
       </c>
       <c r="K62" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>10/2025</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -2970,7 +2970,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -2985,10 +2985,10 @@
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>308</v>
+        <v>453</v>
       </c>
       <c r="K63" t="n">
-        <v>147</v>
+        <v>44</v>
       </c>
     </row>
     <row r="64">
@@ -3031,7 +3031,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3044,7 +3044,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -3059,16 +3059,16 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>453</v>
+        <v>308</v>
       </c>
       <c r="K65" t="n">
-        <v>15</v>
+        <v>147</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -3081,7 +3081,7 @@
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
@@ -3099,13 +3099,13 @@
         <v>453</v>
       </c>
       <c r="K66" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3118,7 +3118,7 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -3136,13 +3136,13 @@
         <v>453</v>
       </c>
       <c r="K67" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -3155,7 +3155,7 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -3173,13 +3173,13 @@
         <v>453</v>
       </c>
       <c r="K68" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3192,7 +3192,7 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -3210,13 +3210,13 @@
         <v>453</v>
       </c>
       <c r="K69" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -3229,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -3247,13 +3247,13 @@
         <v>453</v>
       </c>
       <c r="K70" t="n">
-        <v>3</v>
+        <v>44</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3266,7 +3266,7 @@
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -3284,13 +3284,13 @@
         <v>453</v>
       </c>
       <c r="K71" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -3303,7 +3303,7 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -3321,13 +3321,13 @@
         <v>453</v>
       </c>
       <c r="K72" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3340,7 +3340,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -3358,13 +3358,13 @@
         <v>453</v>
       </c>
       <c r="K73" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -3377,7 +3377,7 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -3395,13 +3395,13 @@
         <v>453</v>
       </c>
       <c r="K74" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3414,7 +3414,7 @@
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
@@ -3432,28 +3432,65 @@
         <v>453</v>
       </c>
       <c r="K75" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>10983</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="n">
+        <v>2</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>453</v>
+      </c>
+      <c r="K76" t="n">
         <v>44</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="4" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B76" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F76" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G76" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H76" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="4" t="n">
+      <c r="B77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3469,7 +3506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K95"/>
+  <dimension ref="A1:K96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5839,57 +5876,57 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>09/2019</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>374658</v>
+        <v>411319</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>-0.08782189716333641</v>
+        <v>0.001436470276021416</v>
       </c>
       <c r="E64" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>272555</v>
+        <v>244817</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0.1133009554075085</v>
+        <v>0.0002940972236405152</v>
       </c>
       <c r="J64" t="n">
-        <v>31236</v>
+        <v>43125</v>
       </c>
       <c r="K64" t="n">
-        <v>8103</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>09/2020</t>
+          <t>09/2019</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>398039</v>
+        <v>374658</v>
       </c>
       <c r="C65" t="n">
         <v>0</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>0.06240624783135553</v>
+        <v>-0.08913033436335302</v>
       </c>
       <c r="E65" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F65" t="n">
         <v>272555</v>
@@ -5901,13 +5938,13 @@
         <v>0</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>0</v>
+        <v>0.1129736329520722</v>
       </c>
       <c r="J65" t="n">
-        <v>26869</v>
+        <v>31236</v>
       </c>
       <c r="K65" t="n">
-        <v>12360</v>
+        <v>8103</v>
       </c>
     </row>
     <row r="66">
@@ -5923,7 +5960,7 @@
         <v>0</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>0</v>
+        <v>0.06240624783135553</v>
       </c>
       <c r="E66" t="n">
         <v>7</v>
@@ -5950,23 +5987,23 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>09/2021</t>
+          <t>09/2020</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>402212</v>
+        <v>398039</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0.01048389730654534</v>
+        <v>0</v>
       </c>
       <c r="E67" t="n">
         <v>7</v>
       </c>
       <c r="F67" t="n">
-        <v>244817</v>
+        <v>272555</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -5975,32 +6012,32 @@
         <v>0</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>-0.1017702848966264</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>39505</v>
+        <v>26869</v>
       </c>
       <c r="K67" t="n">
-        <v>3</v>
+        <v>12360</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>09/2022</t>
+          <t>09/2021</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>401174</v>
+        <v>402212</v>
       </c>
       <c r="C68" t="n">
         <v>0</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>-0.002580728571002357</v>
+        <v>0.01048389730654534</v>
       </c>
       <c r="E68" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F68" t="n">
         <v>244817</v>
@@ -6012,32 +6049,32 @@
         <v>0</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0</v>
+        <v>-0.1017702848966264</v>
       </c>
       <c r="J68" t="n">
-        <v>40236</v>
+        <v>39505</v>
       </c>
       <c r="K68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>09/2023</t>
+          <t>09/2022</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>400097</v>
+        <v>401174</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>-0.002684620638426219</v>
+        <v>-0.002580728571002357</v>
       </c>
       <c r="E69" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F69" t="n">
         <v>244817</v>
@@ -6052,29 +6089,29 @@
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>40819</v>
+        <v>40236</v>
       </c>
       <c r="K69" t="n">
-        <v>178</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>09/2024</t>
+          <t>09/2023</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>400317</v>
+        <v>400097</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0.0005498666573355961</v>
+        <v>-0.002684620638426219</v>
       </c>
       <c r="E70" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F70" t="n">
         <v>244817</v>
@@ -6089,29 +6126,29 @@
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>41350</v>
+        <v>40819</v>
       </c>
       <c r="K70" t="n">
-        <v>254</v>
+        <v>178</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>09/2025</t>
+          <t>09/2024</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>411254</v>
+        <v>400317</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0.02732084822777948</v>
+        <v>0.0005498666573355961</v>
       </c>
       <c r="E71" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F71" t="n">
         <v>244817</v>
@@ -6126,32 +6163,32 @@
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>41345</v>
+        <v>41350</v>
       </c>
       <c r="K71" t="n">
-        <v>1173</v>
+        <v>254</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>10/2019</t>
+          <t>09/2025</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>374658</v>
+        <v>411254</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>-0.08898636852164356</v>
+        <v>0.02732084822777948</v>
       </c>
       <c r="E72" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F72" t="n">
-        <v>272555</v>
+        <v>244817</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -6160,35 +6197,35 @@
         <v>0</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>0.1133009554075085</v>
+        <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>31236</v>
+        <v>41345</v>
       </c>
       <c r="K72" t="n">
-        <v>8103</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>10/2020</t>
+          <t>10/2019</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>398039</v>
+        <v>374658</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0.06240624783135553</v>
+        <v>-0.08898636852164356</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
-        <v>168210</v>
+        <v>272555</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -6197,13 +6234,13 @@
         <v>0</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>-0.3828401607015098</v>
+        <v>0.1133009554075085</v>
       </c>
       <c r="J73" t="n">
-        <v>26868</v>
+        <v>31236</v>
       </c>
       <c r="K73" t="n">
-        <v>12404</v>
+        <v>8103</v>
       </c>
     </row>
     <row r="74">
@@ -6219,7 +6256,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>0</v>
+        <v>0.06240624783135553</v>
       </c>
       <c r="E74" t="n">
         <v>5</v>
@@ -6234,7 +6271,7 @@
         <v>0</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>0</v>
+        <v>-0.3828401607015098</v>
       </c>
       <c r="J74" t="n">
         <v>26868</v>
@@ -6246,23 +6283,23 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>10/2021</t>
+          <t>10/2020</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>402212</v>
+        <v>398039</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.01048389730654534</v>
+        <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F75" t="n">
-        <v>244817</v>
+        <v>168210</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -6271,32 +6308,32 @@
         <v>0</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.4554247666607217</v>
+        <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>39517</v>
+        <v>26868</v>
       </c>
       <c r="K75" t="n">
-        <v>72</v>
+        <v>12404</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>10/2022</t>
+          <t>10/2021</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>401174</v>
+        <v>402212</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>-0.002580728571002357</v>
+        <v>0.01048389730654534</v>
       </c>
       <c r="E76" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F76" t="n">
         <v>244817</v>
@@ -6308,32 +6345,32 @@
         <v>0</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0</v>
+        <v>0.4554247666607217</v>
       </c>
       <c r="J76" t="n">
-        <v>40235</v>
+        <v>39517</v>
       </c>
       <c r="K76" t="n">
-        <v>2</v>
+        <v>72</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>10/2023</t>
+          <t>10/2022</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>400097</v>
+        <v>401174</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>-0.002684620638426219</v>
+        <v>-0.002580728571002357</v>
       </c>
       <c r="E77" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F77" t="n">
         <v>244817</v>
@@ -6348,29 +6385,29 @@
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>40741</v>
+        <v>40235</v>
       </c>
       <c r="K77" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>10/2024</t>
+          <t>10/2023</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>400317</v>
+        <v>400097</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>0.0005498666573355961</v>
+        <v>-0.002684620638426219</v>
       </c>
       <c r="E78" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F78" t="n">
         <v>244817</v>
@@ -6385,26 +6422,26 @@
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>41352</v>
+        <v>40741</v>
       </c>
       <c r="K78" t="n">
-        <v>296</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>10/2025</t>
+          <t>10/2024</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>411319</v>
+        <v>400317</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>0.02748321954850781</v>
+        <v>0.0005498666573355961</v>
       </c>
       <c r="E79" t="n">
         <v>4</v>
@@ -6422,32 +6459,32 @@
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>41345</v>
+        <v>41352</v>
       </c>
       <c r="K79" t="n">
-        <v>1247</v>
+        <v>296</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2025</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>395094</v>
+        <v>411319</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>-0.03944626919738695</v>
+        <v>0.02748321954850781</v>
       </c>
       <c r="E80" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F80" t="n">
-        <v>272555</v>
+        <v>244817</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -6456,35 +6493,35 @@
         <v>0</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>0.1133009554075085</v>
+        <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>26611</v>
+        <v>41345</v>
       </c>
       <c r="K80" t="n">
-        <v>13235</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>398039</v>
+        <v>395094</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>0.007453922357717404</v>
+        <v>-0.03944626919738695</v>
       </c>
       <c r="E81" t="n">
         <v>8</v>
       </c>
       <c r="F81" t="n">
-        <v>244817</v>
+        <v>272555</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -6493,13 +6530,13 @@
         <v>0</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>-0.1017702848966264</v>
+        <v>0.1133009554075085</v>
       </c>
       <c r="J81" t="n">
-        <v>29399</v>
+        <v>26611</v>
       </c>
       <c r="K81" t="n">
-        <v>9655</v>
+        <v>13235</v>
       </c>
     </row>
     <row r="82">
@@ -6515,7 +6552,7 @@
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0</v>
+        <v>0.007453922357717404</v>
       </c>
       <c r="E82" t="n">
         <v>8</v>
@@ -6530,7 +6567,7 @@
         <v>0</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>0</v>
+        <v>-0.1017702848966264</v>
       </c>
       <c r="J82" t="n">
         <v>29399</v>
@@ -6542,20 +6579,20 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>402212</v>
+        <v>398039</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.01048389730654534</v>
+        <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F83" t="n">
         <v>244817</v>
@@ -6570,29 +6607,29 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>39659</v>
+        <v>29399</v>
       </c>
       <c r="K83" t="n">
-        <v>1</v>
+        <v>9655</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>401174</v>
+        <v>402212</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>-0.002580728571002357</v>
+        <v>0.01048389730654534</v>
       </c>
       <c r="E84" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F84" t="n">
         <v>244817</v>
@@ -6607,29 +6644,29 @@
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>40235</v>
+        <v>39659</v>
       </c>
       <c r="K84" t="n">
-        <v>137</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>400097</v>
+        <v>401174</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>-0.002684620638426219</v>
+        <v>-0.002580728571002357</v>
       </c>
       <c r="E85" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F85" t="n">
         <v>244817</v>
@@ -6644,29 +6681,29 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>40758</v>
+        <v>40235</v>
       </c>
       <c r="K85" t="n">
-        <v>85</v>
+        <v>137</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>400317</v>
+        <v>400097</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.0005498666573355961</v>
+        <v>-0.002684620638426219</v>
       </c>
       <c r="E86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F86" t="n">
         <v>244817</v>
@@ -6681,29 +6718,29 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>41352</v>
+        <v>40758</v>
       </c>
       <c r="K86" t="n">
-        <v>405</v>
+        <v>85</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>411319</v>
+        <v>400317</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.02748321954850781</v>
+        <v>0.0005498666573355961</v>
       </c>
       <c r="E87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F87" t="n">
         <v>244817</v>
@@ -6712,75 +6749,75 @@
         <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0.0002940972236405152</v>
+        <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>41344</v>
+        <v>41352</v>
       </c>
       <c r="K87" t="n">
-        <v>1355</v>
+        <v>405</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>395094</v>
+        <v>411319</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>-0.03944626919738695</v>
+        <v>0.02748321954850781</v>
       </c>
       <c r="E88" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="F88" t="n">
-        <v>272555</v>
+        <v>244817</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.1129736329520722</v>
+        <v>0.0002940972236405152</v>
       </c>
       <c r="J88" t="n">
-        <v>26611</v>
+        <v>41344</v>
       </c>
       <c r="K88" t="n">
-        <v>13235</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>398164</v>
+        <v>395094</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.007770302763393015</v>
+        <v>-0.03944626919738695</v>
       </c>
       <c r="E89" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F89" t="n">
-        <v>244817</v>
+        <v>272555</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -6789,32 +6826,32 @@
         <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>-0.1017702848966264</v>
+        <v>0.1129736329520722</v>
       </c>
       <c r="J89" t="n">
-        <v>32472</v>
+        <v>26611</v>
       </c>
       <c r="K89" t="n">
-        <v>6659</v>
+        <v>13235</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>402212</v>
+        <v>398164</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>0.01016666499231472</v>
+        <v>0.007770302763393015</v>
       </c>
       <c r="E90" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F90" t="n">
         <v>244817</v>
@@ -6826,32 +6863,32 @@
         <v>0</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>0</v>
+        <v>-0.1017702848966264</v>
       </c>
       <c r="J90" t="n">
-        <v>39697</v>
+        <v>32472</v>
       </c>
       <c r="K90" t="n">
-        <v>19</v>
+        <v>6659</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>401174</v>
+        <v>402212</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>-0.002580728571002357</v>
+        <v>0.01016666499231472</v>
       </c>
       <c r="E91" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F91" t="n">
         <v>244817</v>
@@ -6866,29 +6903,29 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>40232</v>
+        <v>39697</v>
       </c>
       <c r="K91" t="n">
-        <v>137</v>
+        <v>19</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>400097</v>
+        <v>401174</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>-0.002684620638426219</v>
+        <v>-0.002580728571002357</v>
       </c>
       <c r="E92" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F92" t="n">
         <v>244817</v>
@@ -6903,7 +6940,7 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>40759</v>
+        <v>40232</v>
       </c>
       <c r="K92" t="n">
         <v>137</v>
@@ -6912,23 +6949,23 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>400317</v>
+        <v>400097</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.0005498666573355961</v>
+        <v>-0.002684620638426219</v>
       </c>
       <c r="E93" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F93" t="n">
-        <v>245147</v>
+        <v>244817</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -6937,71 +6974,108 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0.001347945608352361</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>41352</v>
+        <v>40759</v>
       </c>
       <c r="K93" t="n">
-        <v>472</v>
+        <v>137</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>400317</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>0.0005498666573355961</v>
+      </c>
+      <c r="E94" t="n">
+        <v>3</v>
+      </c>
+      <c r="F94" t="n">
+        <v>245147</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3" t="n">
+        <v>0.001347945608352361</v>
+      </c>
+      <c r="J94" t="n">
+        <v>41352</v>
+      </c>
+      <c r="K94" t="n">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
           <t>12/2025</t>
         </is>
       </c>
-      <c r="B94" t="n">
+      <c r="B95" t="n">
         <v>411319</v>
       </c>
-      <c r="C94" t="n">
-        <v>0</v>
-      </c>
-      <c r="D94" s="3" t="n">
+      <c r="C95" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="3" t="n">
         <v>0.02748321954850781</v>
       </c>
-      <c r="E94" t="n">
+      <c r="E95" t="n">
         <v>2</v>
       </c>
-      <c r="F94" t="n">
+      <c r="F95" t="n">
         <v>244817</v>
       </c>
-      <c r="G94" t="n">
-        <v>0</v>
-      </c>
-      <c r="H94" t="n">
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
         <v>72</v>
       </c>
-      <c r="I94" s="3" t="n">
+      <c r="I95" s="3" t="n">
         <v>-0.001052429766629818</v>
       </c>
-      <c r="J94" t="n">
+      <c r="J95" t="n">
         <v>41340</v>
       </c>
-      <c r="K94" t="n">
+      <c r="K95" t="n">
         <v>1427</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="4" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B95" s="4" t="n">
+      <c r="B96" s="4" t="n">
         <v>16225</v>
       </c>
-      <c r="F95" s="4" t="n">
+      <c r="F96" s="4" t="n">
         <v>-27738</v>
       </c>
-      <c r="G95" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" s="4" t="n">
+      <c r="G96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="J95" s="4" t="n">
+      <c r="J96" s="4" t="n">
         <v>14729</v>
       </c>
     </row>
@@ -7017,7 +7091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K95"/>
+  <dimension ref="A1:K96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -9387,23 +9461,23 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>09/2019</t>
+          <t>08/2026</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>88778</v>
+        <v>88522</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0.002891936467770724</v>
+        <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>31012</v>
+        <v>50942</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -9412,19 +9486,19 @@
         <v>0</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>-0.3912292410977189</v>
+        <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>7777</v>
+        <v>9138</v>
       </c>
       <c r="K64" t="n">
-        <v>937</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>09/2020</t>
+          <t>09/2019</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -9434,13 +9508,13 @@
         <v>0</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>0</v>
+        <v>0.002891936467770724</v>
       </c>
       <c r="E65" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F65" t="n">
-        <v>26198</v>
+        <v>31012</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -9449,13 +9523,13 @@
         <v>0</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>-0.1552302334580163</v>
+        <v>-0.3912292410977189</v>
       </c>
       <c r="J65" t="n">
-        <v>7346</v>
+        <v>7777</v>
       </c>
       <c r="K65" t="n">
-        <v>1297</v>
+        <v>937</v>
       </c>
     </row>
     <row r="66">
@@ -9486,7 +9560,7 @@
         <v>0</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>0</v>
+        <v>-0.1552302334580163</v>
       </c>
       <c r="J66" t="n">
         <v>7346</v>
@@ -9498,23 +9572,23 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>09/2021</t>
+          <t>09/2020</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>90643</v>
+        <v>88778</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0.02100745680236095</v>
+        <v>0</v>
       </c>
       <c r="E67" t="n">
         <v>7</v>
       </c>
       <c r="F67" t="n">
-        <v>50942</v>
+        <v>26198</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -9523,19 +9597,19 @@
         <v>0</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0.9444995801206199</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>8225</v>
+        <v>7346</v>
       </c>
       <c r="K67" t="n">
-        <v>1</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>09/2022</t>
+          <t>09/2021</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -9545,10 +9619,10 @@
         <v>0</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0</v>
+        <v>0.02100745680236095</v>
       </c>
       <c r="E68" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F68" t="n">
         <v>50942</v>
@@ -9560,32 +9634,32 @@
         <v>0</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0</v>
+        <v>0.9444995801206199</v>
       </c>
       <c r="J68" t="n">
-        <v>8354</v>
+        <v>8225</v>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>09/2023</t>
+          <t>09/2022</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>88522</v>
+        <v>90643</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>-0.0233994903081319</v>
+        <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F69" t="n">
         <v>50942</v>
@@ -9600,7 +9674,7 @@
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>8602</v>
+        <v>8354</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -9609,7 +9683,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>09/2024</t>
+          <t>09/2023</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -9619,13 +9693,13 @@
         <v>0</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>-0.0233994903081319</v>
       </c>
       <c r="E70" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F70" t="n">
-        <v>46301</v>
+        <v>50942</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -9634,10 +9708,10 @@
         <v>0</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>-0.09110360802481253</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>8790</v>
+        <v>8602</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -9646,7 +9720,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>09/2025</t>
+          <t>09/2024</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -9659,10 +9733,10 @@
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F71" t="n">
-        <v>50942</v>
+        <v>46301</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -9671,10 +9745,10 @@
         <v>0</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0.1002354160817261</v>
+        <v>-0.09110360802481253</v>
       </c>
       <c r="J71" t="n">
-        <v>8986</v>
+        <v>8790</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
@@ -9683,23 +9757,23 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>10/2019</t>
+          <t>09/2025</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>88778</v>
+        <v>88522</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>0.002891936467770724</v>
+        <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F72" t="n">
-        <v>31012</v>
+        <v>50942</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -9708,19 +9782,19 @@
         <v>0</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>-0.3912292410977189</v>
+        <v>0.1002354160817261</v>
       </c>
       <c r="J72" t="n">
-        <v>7777</v>
+        <v>8986</v>
       </c>
       <c r="K72" t="n">
-        <v>937</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>10/2020</t>
+          <t>10/2019</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -9730,13 +9804,13 @@
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0</v>
+        <v>0.002891936467770724</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
-        <v>26198</v>
+        <v>31012</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -9745,13 +9819,13 @@
         <v>0</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>-0.1552302334580163</v>
+        <v>-0.3912292410977189</v>
       </c>
       <c r="J73" t="n">
-        <v>7346</v>
+        <v>7777</v>
       </c>
       <c r="K73" t="n">
-        <v>1310</v>
+        <v>937</v>
       </c>
     </row>
     <row r="74">
@@ -9782,7 +9856,7 @@
         <v>0</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>0</v>
+        <v>-0.1552302334580163</v>
       </c>
       <c r="J74" t="n">
         <v>7346</v>
@@ -9794,23 +9868,23 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>10/2021</t>
+          <t>10/2020</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>90643</v>
+        <v>88778</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.02100745680236095</v>
+        <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F75" t="n">
-        <v>50942</v>
+        <v>26198</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -9819,19 +9893,19 @@
         <v>0</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.9444995801206199</v>
+        <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>8234</v>
+        <v>7346</v>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>10/2022</t>
+          <t>10/2021</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -9841,10 +9915,10 @@
         <v>0</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>0</v>
+        <v>0.02100745680236095</v>
       </c>
       <c r="E76" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F76" t="n">
         <v>50942</v>
@@ -9856,32 +9930,32 @@
         <v>0</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0</v>
+        <v>0.9444995801206199</v>
       </c>
       <c r="J76" t="n">
-        <v>8382</v>
+        <v>8234</v>
       </c>
       <c r="K76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>10/2023</t>
+          <t>10/2022</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>88522</v>
+        <v>90643</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>-0.0233994903081319</v>
+        <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F77" t="n">
         <v>50942</v>
@@ -9896,16 +9970,16 @@
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>8513</v>
+        <v>8382</v>
       </c>
       <c r="K77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>10/2024</t>
+          <t>10/2023</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -9915,10 +9989,10 @@
         <v>0</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>0</v>
+        <v>-0.0233994903081319</v>
       </c>
       <c r="E78" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F78" t="n">
         <v>50942</v>
@@ -9933,7 +10007,7 @@
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>8808</v>
+        <v>8513</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
@@ -9942,7 +10016,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>10/2025</t>
+          <t>10/2024</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -9970,7 +10044,7 @@
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>9007</v>
+        <v>8808</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
@@ -9979,23 +10053,23 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2025</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>88778</v>
+        <v>88522</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>0.002891936467770724</v>
+        <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F80" t="n">
-        <v>26198</v>
+        <v>50942</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -10004,19 +10078,19 @@
         <v>0</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>-0.4857288681245338</v>
+        <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>7708</v>
+        <v>9007</v>
       </c>
       <c r="K80" t="n">
-        <v>1218</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -10026,13 +10100,13 @@
         <v>0</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>0</v>
+        <v>0.002891936467770724</v>
       </c>
       <c r="E81" t="n">
         <v>8</v>
       </c>
       <c r="F81" t="n">
-        <v>50942</v>
+        <v>26198</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -10041,13 +10115,13 @@
         <v>0</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>0.9444995801206199</v>
+        <v>-0.4857288681245338</v>
       </c>
       <c r="J81" t="n">
-        <v>8068</v>
+        <v>7708</v>
       </c>
       <c r="K81" t="n">
-        <v>8</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="82">
@@ -10078,7 +10152,7 @@
         <v>0</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>0</v>
+        <v>0.9444995801206199</v>
       </c>
       <c r="J82" t="n">
         <v>8068</v>
@@ -10090,20 +10164,20 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>90643</v>
+        <v>88778</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.02100745680236095</v>
+        <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F83" t="n">
         <v>50942</v>
@@ -10118,16 +10192,16 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>8243</v>
+        <v>8068</v>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -10137,10 +10211,10 @@
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0</v>
+        <v>0.02100745680236095</v>
       </c>
       <c r="E84" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F84" t="n">
         <v>50942</v>
@@ -10155,7 +10229,7 @@
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>8396</v>
+        <v>8243</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
@@ -10164,20 +10238,20 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>88522</v>
+        <v>90643</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>-0.0233994903081319</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F85" t="n">
         <v>50942</v>
@@ -10192,16 +10266,16 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>8539</v>
+        <v>8396</v>
       </c>
       <c r="K85" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -10211,10 +10285,10 @@
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0</v>
+        <v>-0.0233994903081319</v>
       </c>
       <c r="E86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F86" t="n">
         <v>50942</v>
@@ -10229,16 +10303,16 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>8824</v>
+        <v>8539</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -10251,7 +10325,7 @@
         <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F87" t="n">
         <v>50942</v>
@@ -10266,7 +10340,7 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>9019</v>
+        <v>8824</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -10275,23 +10349,23 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>88778</v>
+        <v>88522</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.002891936467770724</v>
+        <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="F88" t="n">
-        <v>26198</v>
+        <v>50942</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -10300,19 +10374,19 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>-0.4857288681245338</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>7708</v>
+        <v>9019</v>
       </c>
       <c r="K88" t="n">
-        <v>1218</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -10322,13 +10396,13 @@
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0</v>
+        <v>0.002891936467770724</v>
       </c>
       <c r="E89" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F89" t="n">
-        <v>50942</v>
+        <v>26198</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -10337,32 +10411,32 @@
         <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.9444995801206199</v>
+        <v>-0.4857288681245338</v>
       </c>
       <c r="J89" t="n">
-        <v>8082</v>
+        <v>7708</v>
       </c>
       <c r="K89" t="n">
-        <v>2</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>90643</v>
+        <v>88778</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>0.02100745680236095</v>
+        <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F90" t="n">
         <v>50942</v>
@@ -10374,19 +10448,19 @@
         <v>0</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>0</v>
+        <v>0.9444995801206199</v>
       </c>
       <c r="J90" t="n">
-        <v>8259</v>
+        <v>8082</v>
       </c>
       <c r="K90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -10396,10 +10470,10 @@
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>0.02100745680236095</v>
       </c>
       <c r="E91" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F91" t="n">
         <v>50942</v>
@@ -10414,7 +10488,7 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>8417</v>
+        <v>8259</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
@@ -10423,20 +10497,20 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>88522</v>
+        <v>90643</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>-0.0233994903081319</v>
+        <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F92" t="n">
         <v>50942</v>
@@ -10451,7 +10525,7 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>8578</v>
+        <v>8417</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -10460,7 +10534,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -10470,10 +10544,10 @@
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0</v>
+        <v>-0.0233994903081319</v>
       </c>
       <c r="E93" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F93" t="n">
         <v>50942</v>
@@ -10488,7 +10562,7 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>8836</v>
+        <v>8578</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -10497,7 +10571,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -10510,7 +10584,7 @@
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F94" t="n">
         <v>50942</v>
@@ -10525,31 +10599,68 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
+        <v>8836</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>88522</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" t="n">
+        <v>2</v>
+      </c>
+      <c r="F95" t="n">
+        <v>50942</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
         <v>9022</v>
       </c>
-      <c r="K94" t="n">
+      <c r="K95" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="4" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B95" s="4" t="n">
+      <c r="B96" s="4" t="n">
         <v>-256</v>
       </c>
-      <c r="F95" s="4" t="n">
+      <c r="F96" s="4" t="n">
         <v>24744</v>
       </c>
-      <c r="G95" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" s="4" t="n">
+      <c r="G96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" s="4" t="n">
         <v>1314</v>
       </c>
     </row>

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -2452,7 +2452,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -5889,7 +5889,7 @@
         <v>0.001436470276021416</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>244817</v>
@@ -9474,7 +9474,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>50942</v>

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -5907,7 +5907,7 @@
         <v>43125</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -9492,7 +9492,7 @@
         <v>9138</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -5907,7 +5907,7 @@
         <v>43125</v>
       </c>
       <c r="K64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -9492,7 +9492,7 @@
         <v>9138</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -5904,10 +5904,10 @@
         <v>0.0002940972236405152</v>
       </c>
       <c r="J64" t="n">
-        <v>43125</v>
+        <v>43161</v>
       </c>
       <c r="K64" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -9489,10 +9489,10 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>9138</v>
+        <v>9143</v>
       </c>
       <c r="K64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -5907,7 +5907,7 @@
         <v>43161</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65">
@@ -9492,7 +9492,7 @@
         <v>9143</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -5907,7 +5907,7 @@
         <v>43161</v>
       </c>
       <c r="K64" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -5880,13 +5880,13 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>411319</v>
+        <v>400316</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0.001436470276021416</v>
+        <v>-0.02535248302408644</v>
       </c>
       <c r="E64" t="n">
         <v>1</v>
@@ -5904,10 +5904,10 @@
         <v>0.0002940972236405152</v>
       </c>
       <c r="J64" t="n">
-        <v>43161</v>
+        <v>43176</v>
       </c>
       <c r="K64" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -5923,7 +5923,7 @@
         <v>0</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>-0.08913033436335302</v>
+        <v>-0.06409436545129348</v>
       </c>
       <c r="E65" t="n">
         <v>5</v>
@@ -9492,7 +9492,7 @@
         <v>9143</v>
       </c>
       <c r="K64" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -2452,7 +2452,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -5880,16 +5880,16 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>400316</v>
+        <v/>
       </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>-0.02535248302408644</v>
+        <v/>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F64" t="n">
         <v>244817</v>
@@ -5904,7 +5904,7 @@
         <v>0.0002940972236405152</v>
       </c>
       <c r="J64" t="n">
-        <v>43176</v>
+        <v>43177</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -5923,7 +5923,7 @@
         <v>0</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>-0.06409436545129348</v>
+        <v/>
       </c>
       <c r="E65" t="n">
         <v>5</v>
@@ -9474,7 +9474,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F64" t="n">
         <v>50942</v>
@@ -9492,7 +9492,7 @@
         <v>9143</v>
       </c>
       <c r="K64" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -2452,7 +2452,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -5880,16 +5880,16 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v/>
+        <v>400054</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v/>
+        <v>-0.02599037321445527</v>
       </c>
       <c r="E64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F64" t="n">
         <v>244817</v>
@@ -5904,7 +5904,7 @@
         <v>0.0002940972236405152</v>
       </c>
       <c r="J64" t="n">
-        <v>43177</v>
+        <v>43182</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -5923,7 +5923,7 @@
         <v>0</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v/>
+        <v>-0.06348143000694906</v>
       </c>
       <c r="E65" t="n">
         <v>5</v>
@@ -9474,7 +9474,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F64" t="n">
         <v>50942</v>

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -5907,7 +5907,7 @@
         <v>43182</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -9489,10 +9489,10 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>9143</v>
+        <v>9157</v>
       </c>
       <c r="K64" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroCMA.xlsx
+++ b/regionais/registroCMA.xlsx
@@ -5907,7 +5907,7 @@
         <v>43182</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65">
